--- a/artfynd/A 56075-2023 artfynd.xlsx
+++ b/artfynd/A 56075-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56075-2023 artfynd.xlsx
+++ b/artfynd/A 56075-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106188460</v>
+        <v>106188453</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604299.105352231</v>
+        <v>604405</v>
       </c>
       <c r="R2" t="n">
-        <v>6670411.412070801</v>
+        <v>6670383</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106188453</v>
+        <v>106188454</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604405.1912497459</v>
+        <v>604395</v>
       </c>
       <c r="R3" t="n">
-        <v>6670383.050921252</v>
+        <v>6670399</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,19 +844,9 @@
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106188452</v>
+        <v>106222508</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljusbäck, Upl</t>
+          <t>Nordmyrasjön söder om, Rönnholmen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604357.2031129586</v>
+        <v>604410</v>
       </c>
       <c r="R4" t="n">
-        <v>6670386.167383562</v>
+        <v>6670380</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,19 +945,9 @@
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,31 +962,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106188454</v>
+        <v>106222509</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,17 +1005,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljusbäck, Upl</t>
+          <t>Nordmyrasjön söder om, Rönnholmen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604395.2652050536</v>
+        <v>604406</v>
       </c>
       <c r="R5" t="n">
-        <v>6670398.708029591</v>
+        <v>6670395</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,19 +1042,9 @@
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-01-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,69 +1059,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106222507</v>
+        <v>106188452</v>
       </c>
       <c r="B6" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nordmyrasjön söder om, Rönnholmen, Upl</t>
+          <t>Ljusbäck, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604404.5604186336</v>
+        <v>604357</v>
       </c>
       <c r="R6" t="n">
-        <v>6670352.64744375</v>
+        <v>6670386</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,21 +1139,11 @@
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,73 +1152,52 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>I stort sett död ek</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Quercus robur # I stort sett död ek</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karin Wiklund, Johan Lilja, Cecilia Ronnås, sonja Preuss</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106222509</v>
+        <v>106222507</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604405.8480845428</v>
+        <v>604405</v>
       </c>
       <c r="R7" t="n">
-        <v>6670395.024516783</v>
+        <v>6670353</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,21 +1240,11 @@
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-01-27</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1367,6 +1253,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>I stort sett död ek</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Quercus robur # I stort sett död ek</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1376,60 +1282,64 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Karin Wiklund, Johan Lilja, Cecilia Ronnås, sonja Preuss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106222508</v>
+        <v>106224560</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordmyrasjön söder om, Rönnholmen, Upl</t>
+          <t>Rönnholmen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604409.2788781644</v>
+        <v>604371</v>
       </c>
       <c r="R8" t="n">
-        <v>6670379.680510092</v>
+        <v>6670376</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1368,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1378,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,55 +1387,70 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karin Wiklund</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106224560</v>
+        <v>106188645</v>
       </c>
       <c r="B9" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>102204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1544,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604371.4742402935</v>
+        <v>604200</v>
       </c>
       <c r="R9" t="n">
-        <v>6670375.615074436</v>
+        <v>6670432</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1579,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,21 +1527,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1629,6 +1539,107 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>106188460</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ljusbäck, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>604299</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6670412</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-01-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>

--- a/artfynd/A 56075-2023 artfynd.xlsx
+++ b/artfynd/A 56075-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106188453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106188454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106222508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106222509</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106188452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106222507</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106224560</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106188645</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,8 +1689,24 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106188460</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>